--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
@@ -521,7 +521,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -530,10 +530,10 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>76.92</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -547,7 +547,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -556,13 +556,13 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>82.5</v>
+        <v>82.05</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -619,10 +619,10 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -631,7 +631,7 @@
         <v>13</v>
       </c>
       <c r="G7">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="H7">
         <v>7.2</v>
@@ -759,13 +759,13 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -782,13 +782,13 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -848,10 +848,10 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>18</v>
@@ -982,7 +982,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -991,10 +991,10 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>76.92</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -1008,7 +1008,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1017,13 +1017,13 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>82.5</v>
+        <v>82.05</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1080,10 +1080,10 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
       <c r="G7">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="H7">
         <v>7.2</v>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
@@ -671,10 +671,10 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>31</v>
       </c>
       <c r="G9">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>9.199999999999999</v>
@@ -894,10 +894,10 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E9">
         <v>31</v>
@@ -1132,10 +1132,10 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>31</v>
       </c>
       <c r="G9">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>9.199999999999999</v>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -91,13 +91,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ANA ISABEL</t>
   </si>
 </sst>
 </file>
@@ -521,7 +527,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -530,10 +536,10 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>76.31999999999999</v>
+        <v>76.92</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -622,10 +628,10 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>13</v>
@@ -634,7 +640,7 @@
         <v>68.42</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -739,16 +745,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -759,19 +768,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.87</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -828,16 +840,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>75.68000000000001</v>
+      </c>
+      <c r="H6">
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -851,16 +866,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H7">
+        <v>7.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -874,16 +892,19 @@
         <v>38</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>38</v>
       </c>
-      <c r="E8">
-        <v>38</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -897,16 +918,19 @@
         <v>31</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>31</v>
       </c>
-      <c r="E9">
-        <v>31</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -962,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -982,22 +1006,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>76.31999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1060,16 +1084,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>81.08</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1083,19 +1107,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1121,7 +1145,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1147,7 +1171,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
@@ -1157,7 +1181,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1189,7 +1213,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920244</v>
+        <v>23330051920199</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -1198,15 +1222,38 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920302</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
@@ -797,16 +797,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>74.36</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1038,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>82.05</v>
+        <v>74.36</v>
       </c>
       <c r="H4">
         <v>6.7</v>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -89,21 +89,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANA ISABEL</t>
   </si>
 </sst>
 </file>
@@ -989,16 +974,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1024,7 +1009,7 @@
         <v>94.87</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1041,13 +1026,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="H4">
         <v>6.7</v>
@@ -1087,16 +1072,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>75.68000000000001</v>
+        <v>72.97</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1184,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1214,52 +1199,6 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920199</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920302</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
@@ -564,16 +564,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="G5">
+        <v>94.87</v>
+      </c>
+      <c r="H5">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -805,16 +811,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="G5">
+        <v>94.87</v>
+      </c>
+      <c r="H5">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1046,16 +1058,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="G5">
+        <v>94.87</v>
+      </c>
+      <c r="H5">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
@@ -995,7 +995,7 @@
         <v>83.33</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1021,7 +1021,7 @@
         <v>94.87</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1047,7 +1047,7 @@
         <v>84.62</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1099,7 +1099,7 @@
         <v>72.97</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1125,7 +1125,7 @@
         <v>78.95</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1151,7 +1151,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1177,7 +1177,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20231.xlsx
@@ -995,7 +995,7 @@
         <v>83.33</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1021,7 +1021,7 @@
         <v>94.87</v>
       </c>
       <c r="H3">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1047,7 +1047,7 @@
         <v>84.62</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1099,7 +1099,7 @@
         <v>72.97</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1125,7 +1125,7 @@
         <v>78.95</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1151,7 +1151,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1177,7 +1177,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
